--- a/output/pdf_financials_xlsx/SCRI.xlsx
+++ b/output/pdf_financials_xlsx/SCRI.xlsx
@@ -1423,7 +1423,7 @@
         <v>0</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.044728</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0</v>
@@ -1467,7 +1467,7 @@
         <v>0</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.044728</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0</v>
@@ -1731,7 +1731,7 @@
         <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.145891</v>
+        <v>0.101163</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.404451</v>
@@ -7566,7 +7566,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">

--- a/output/pdf_financials_xlsx/SCRI.xlsx
+++ b/output/pdf_financials_xlsx/SCRI.xlsx
@@ -1555,7 +1555,7 @@
         <v>0</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="D40" s="3" t="n">
         <v>0</v>
@@ -1577,7 +1577,7 @@
         <v>0.001</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>0.130938</v>
@@ -1731,7 +1731,7 @@
         <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.101163</v>
+        <v>0.096163</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.404451</v>
